--- a/docs/downloads/20260902_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20260902_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -1395,11 +1395,7 @@
         <f>Z11/$D$11</f>
         <v/>
       </c>
-      <c r="AB11" s="8" t="inlineStr">
-        <is>
-          <t>Not yet launched</t>
-        </is>
-      </c>
+      <c r="AB11" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="7">
